--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E8" s="3">
         <v>40800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>42000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E9" s="3">
         <v>8000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8000</v>
       </c>
-      <c r="G9" s="3">
-        <v>9700</v>
-      </c>
       <c r="H9" s="3">
-        <v>6600</v>
+        <v>7800</v>
       </c>
       <c r="I9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J9" s="3">
         <v>5300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E10" s="3">
         <v>32800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>34300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>34200</v>
       </c>
-      <c r="G10" s="3">
-        <v>40100</v>
-      </c>
       <c r="H10" s="3">
-        <v>26500</v>
+        <v>42000</v>
       </c>
       <c r="I10" s="3">
+        <v>20400</v>
+      </c>
+      <c r="J10" s="3">
         <v>24700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>16800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E12" s="3">
         <v>4400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1900</v>
       </c>
       <c r="O12" s="3">
         <v>1900</v>
       </c>
       <c r="P12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1500</v>
       </c>
       <c r="T12" s="3">
         <v>1500</v>
       </c>
       <c r="U12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1096,21 +1115,21 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>4500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1126,8 +1145,8 @@
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E17" s="3">
         <v>58600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>55000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>56000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3600</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,34 +1410,35 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1420,67 +1453,70 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5300</v>
       </c>
       <c r="L21" s="3">
         <v>-5300</v>
       </c>
       <c r="M21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1502,8 +1538,11 @@
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1520,13 +1559,13 @@
         <v>1300</v>
       </c>
       <c r="H22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>1000</v>
@@ -1541,93 +1580,99 @@
         <v>1000</v>
       </c>
       <c r="O22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
       </c>
       <c r="V22" s="3">
+        <v>200</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1688,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,34 +2188,37 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2164,90 +2233,96 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,47 +2570,48 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>98500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>109500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>119600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2538,8 +2624,8 @@
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
+      <c r="T41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -2547,26 +2633,29 @@
       <c r="V41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E42" s="3">
         <v>114900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>127400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>141000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>61800</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2582,8 +2671,8 @@
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2609,47 +2698,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E43" s="3">
         <v>25000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2662,8 +2754,8 @@
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2671,47 +2763,50 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E44" s="3">
         <v>29300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7400</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2724,8 +2819,8 @@
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2733,47 +2828,50 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E45" s="3">
         <v>10700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4000</v>
       </c>
       <c r="I45" s="3">
         <v>4000</v>
       </c>
       <c r="J45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2786,8 +2884,8 @@
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -2795,47 +2893,50 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E46" s="3">
         <v>187100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>198100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>223100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>133400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>135200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>127300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>138000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>135400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>140800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2848,8 +2949,8 @@
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
+      <c r="T46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U46" s="3">
         <v>0</v>
@@ -2857,8 +2958,11 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2919,47 +3023,50 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E48" s="3">
         <v>31000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2972,8 +3079,8 @@
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2981,20 +3088,23 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E49" s="3">
         <v>22100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22300</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3010,8 +3120,8 @@
       <c r="K49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3179,10 +3298,10 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3193,8 +3312,8 @@
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>16</v>
+      <c r="K52" s="3">
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>16</v>
@@ -3211,8 +3330,8 @@
       <c r="P52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,47 +3413,50 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E54" s="3">
         <v>240400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>249600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>249200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>159000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>156400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>158700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>146500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>140800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>142300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3344,8 +3469,8 @@
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
+      <c r="T54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U54" s="3">
         <v>0</v>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,47 +3530,48 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E57" s="3">
         <v>8700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3454,8 +3584,8 @@
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3463,8 +3593,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3525,47 +3658,50 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E59" s="3">
         <v>24500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3578,8 +3714,8 @@
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -3587,47 +3723,50 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3640,8 +3779,8 @@
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
+      <c r="T60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U60" s="3">
         <v>0</v>
@@ -3649,47 +3788,50 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>52900</v>
+        <v>53000</v>
       </c>
       <c r="E61" s="3">
         <v>52900</v>
       </c>
       <c r="F61" s="3">
+        <v>52900</v>
+      </c>
+      <c r="G61" s="3">
         <v>52800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52700</v>
-      </c>
-      <c r="H61" s="3">
-        <v>52600</v>
       </c>
       <c r="I61" s="3">
         <v>52600</v>
       </c>
       <c r="J61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="K61" s="3">
         <v>29400</v>
       </c>
       <c r="L61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="M61" s="3">
         <v>29300</v>
       </c>
       <c r="N61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="O61" s="3">
         <v>29200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3711,34 +3853,37 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E62" s="3">
         <v>16400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>15500</v>
       </c>
       <c r="G62" s="3">
         <v>15500</v>
       </c>
       <c r="H62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I62" s="3">
         <v>19000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14900</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
@@ -3749,8 +3894,8 @@
       <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>16</v>
+      <c r="O62" s="3">
+        <v>200</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>16</v>
@@ -3764,8 +3909,8 @@
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,47 +4113,50 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E66" s="3">
         <v>102500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>98500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>94200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>87000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4012,8 +4169,8 @@
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
+      <c r="T66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U66" s="3">
         <v>0</v>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4205,11 +4372,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>7900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,47 +4463,50 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-134200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-128000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-110400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-98200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-84700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-80300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-68200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-50900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-41900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-35300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-28900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4346,8 +4519,8 @@
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,8 +4723,11 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4550,38 +4735,38 @@
         <v>137900</v>
       </c>
       <c r="E76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="F76" s="3">
         <v>150000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>157600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>60500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>86800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>93100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>97400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-8600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4594,8 +4779,8 @@
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
+      <c r="T76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U76" s="3">
         <v>0</v>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,46 +5015,47 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>900</v>
       </c>
       <c r="G83" s="3">
         <v>900</v>
       </c>
       <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
+      <c r="O83" s="3">
+        <v>100</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
@@ -4871,8 +5069,8 @@
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,47 +5403,50 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5243,8 +5459,8 @@
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -5252,8 +5468,11 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,47 +5495,48 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-900</v>
       </c>
       <c r="L91" s="3">
         <v>-900</v>
       </c>
       <c r="M91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5329,8 +5549,8 @@
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5338,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,47 +5688,50 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-900</v>
       </c>
       <c r="L94" s="3">
         <v>-900</v>
       </c>
       <c r="M94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5515,8 +5744,8 @@
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5524,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,8 +6038,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5805,38 +6050,38 @@
         <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>107900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>107800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5849,8 +6094,8 @@
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -5858,8 +6103,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,47 +6168,50 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-69100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>103400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1900</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5973,13 +6224,16 @@
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E8" s="3">
         <v>62200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E9" s="3">
         <v>11500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E10" s="3">
         <v>50700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>32800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>34300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>34200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>42000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E12" s="3">
         <v>4200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1900</v>
       </c>
       <c r="P12" s="3">
         <v>1900</v>
       </c>
       <c r="Q12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1500</v>
       </c>
       <c r="U12" s="3">
         <v>1500</v>
       </c>
       <c r="V12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,13 +1121,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1118,21 +1138,21 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>4500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1148,8 +1168,8 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E17" s="3">
         <v>69000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>55000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3600</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,37 +1444,38 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1456,70 +1490,73 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-5300</v>
       </c>
       <c r="M21" s="3">
         <v>-5300</v>
       </c>
       <c r="N21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1541,8 +1578,11 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1562,13 +1602,13 @@
         <v>1300</v>
       </c>
       <c r="I22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1000</v>
       </c>
       <c r="L22" s="3">
         <v>1000</v>
@@ -1583,96 +1623,102 @@
         <v>1000</v>
       </c>
       <c r="P22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
       </c>
       <c r="W22" s="3">
+        <v>200</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,37 +2258,40 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2236,93 +2306,99 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,50 +2657,51 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>101500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>109500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>119600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2627,8 +2714,8 @@
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
+      <c r="U41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V41" s="3">
         <v>0</v>
@@ -2636,29 +2723,32 @@
       <c r="W41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E42" s="3">
         <v>110200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>114900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>127400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>141000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>61800</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2674,8 +2764,8 @@
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2701,50 +2791,53 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E43" s="3">
         <v>38100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2757,8 +2850,8 @@
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2766,50 +2859,53 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E44" s="3">
         <v>29200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>29300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7400</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2822,8 +2918,8 @@
       <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2831,50 +2927,53 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E45" s="3">
         <v>7900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4000</v>
       </c>
       <c r="J45" s="3">
         <v>4000</v>
       </c>
       <c r="K45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2887,8 +2986,8 @@
       <c r="T45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -2896,50 +2995,53 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E46" s="3">
         <v>198400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>187100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>198100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>223100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>133400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>127900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>135200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>138000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>135400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>140800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2952,8 +3054,8 @@
       <c r="T46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
+      <c r="U46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V46" s="3">
         <v>0</v>
@@ -2961,8 +3063,11 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3026,50 +3131,53 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E48" s="3">
         <v>31600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3082,8 +3190,8 @@
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3091,23 +3199,26 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E49" s="3">
         <v>21800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3123,8 +3234,8 @@
       <c r="L49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3301,10 +3421,10 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3315,8 +3435,8 @@
       <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>16</v>
+      <c r="L52" s="3">
+        <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>16</v>
@@ -3333,8 +3453,8 @@
       <c r="Q52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,50 +3539,53 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E54" s="3">
         <v>251900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>240400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>249600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>249200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>159000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>156400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>158700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>146500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>140800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>137600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>142300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3472,8 +3598,8 @@
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
+      <c r="U54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V54" s="3">
         <v>0</v>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,50 +3661,51 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E57" s="3">
         <v>11800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3587,8 +3718,8 @@
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3661,50 +3795,53 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E59" s="3">
         <v>33200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3717,8 +3854,8 @@
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -3726,50 +3863,53 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E60" s="3">
         <v>45000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3782,8 +3922,8 @@
       <c r="T60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
+      <c r="U60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V60" s="3">
         <v>0</v>
@@ -3791,50 +3931,53 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E61" s="3">
         <v>53000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>52900</v>
       </c>
       <c r="F61" s="3">
         <v>52900</v>
       </c>
       <c r="G61" s="3">
+        <v>52900</v>
+      </c>
+      <c r="H61" s="3">
         <v>52800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>52700</v>
-      </c>
-      <c r="I61" s="3">
-        <v>52600</v>
       </c>
       <c r="J61" s="3">
         <v>52600</v>
       </c>
       <c r="K61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="L61" s="3">
         <v>29400</v>
       </c>
       <c r="M61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="N61" s="3">
         <v>29300</v>
       </c>
       <c r="O61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="P61" s="3">
         <v>29200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3856,37 +3999,40 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E62" s="3">
         <v>15900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15500</v>
       </c>
       <c r="H62" s="3">
         <v>15500</v>
       </c>
       <c r="I62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="J62" s="3">
         <v>19000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>200</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
@@ -3897,8 +4043,8 @@
       <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>16</v>
+      <c r="P62" s="3">
+        <v>200</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>16</v>
@@ -3912,8 +4058,8 @@
       <c r="T62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,50 +4271,53 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E66" s="3">
         <v>114000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>102500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>94200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>87000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4172,8 +4330,8 @@
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U66" s="3">
-        <v>0</v>
+      <c r="U66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V66" s="3">
         <v>0</v>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4375,11 +4543,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>7900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,50 +4637,53 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-152900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-134200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-128000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-110400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-98200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-84700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-80300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-68200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-50900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-41900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-28900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-23800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4522,8 +4696,8 @@
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,50 +4909,53 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>137900</v>
+        <v>126400</v>
       </c>
       <c r="E76" s="3">
         <v>137900</v>
       </c>
       <c r="F76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="G76" s="3">
         <v>150000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>157600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>86800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>93100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>97400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>102900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-8600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4782,8 +4968,8 @@
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
+      <c r="U76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V76" s="3">
         <v>0</v>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,49 +5214,50 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>900</v>
       </c>
       <c r="I83" s="3">
+        <v>900</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
+      <c r="P83" s="3">
+        <v>100</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
@@ -5072,8 +5271,8 @@
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,50 +5620,53 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5462,8 +5679,8 @@
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,50 +5716,51 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-900</v>
       </c>
       <c r="M91" s="3">
         <v>-900</v>
       </c>
       <c r="N91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5552,8 +5773,8 @@
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,50 +5918,53 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>5000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-80500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-900</v>
       </c>
       <c r="M94" s="3">
         <v>-900</v>
       </c>
       <c r="N94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5747,8 +5977,8 @@
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,50 +6284,53 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="E100" s="3">
         <v>200</v>
       </c>
       <c r="F100" s="3">
+        <v>200</v>
+      </c>
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>107900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>107800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6097,8 +6343,8 @@
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,50 +6420,53 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-69100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>103400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6227,13 +6479,16 @@
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E8" s="3">
         <v>51100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E10" s="3">
         <v>41000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>34300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E12" s="3">
         <v>5300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1900</v>
       </c>
       <c r="Q12" s="3">
         <v>1900</v>
       </c>
       <c r="R12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1500</v>
       </c>
       <c r="V12" s="3">
         <v>1500</v>
       </c>
       <c r="W12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,16 +1141,19 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1141,21 +1161,21 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>4500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1171,8 +1191,8 @@
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E17" s="3">
         <v>70100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>69000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>58600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>55000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>53600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3600</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1445,40 +1478,41 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1493,73 +1527,76 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-5300</v>
       </c>
       <c r="N21" s="3">
         <v>-5300</v>
       </c>
       <c r="O21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="P21" s="3">
         <v>-3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1581,8 +1618,11 @@
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1605,13 +1645,13 @@
         <v>1300</v>
       </c>
       <c r="J22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1000</v>
       </c>
       <c r="M22" s="3">
         <v>1000</v>
@@ -1626,99 +1666,105 @@
         <v>1000</v>
       </c>
       <c r="Q22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R22" s="3">
         <v>1100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
-      </c>
-      <c r="V22" s="3">
-        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,40 +2328,43 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2309,96 +2379,102 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,53 +2744,54 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>88500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>109500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>119600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2717,8 +2804,8 @@
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
+      <c r="V41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -2726,32 +2813,35 @@
       <c r="X41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E42" s="3">
         <v>100700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>110200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>114900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>127400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>141000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>61800</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2767,8 +2857,8 @@
       <c r="O42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2794,53 +2884,56 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E43" s="3">
         <v>30100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>38100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2853,8 +2946,8 @@
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2862,53 +2955,56 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E44" s="3">
         <v>35900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>29200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>29300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7400</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2921,8 +3017,8 @@
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -2930,53 +3026,56 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E45" s="3">
         <v>11400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4000</v>
       </c>
       <c r="K45" s="3">
         <v>4000</v>
       </c>
       <c r="L45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2989,8 +3088,8 @@
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -2998,53 +3097,56 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171600</v>
+      </c>
+      <c r="E46" s="3">
         <v>187400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>198400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>198100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>223100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>133400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>127900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>135200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>138000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>135400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>140800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3057,8 +3159,8 @@
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
+      <c r="V46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,53 +3239,56 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E48" s="3">
         <v>33600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3193,8 +3301,8 @@
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3202,26 +3310,29 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E49" s="3">
         <v>21600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3237,8 +3348,8 @@
       <c r="M49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3424,10 +3544,10 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -3438,8 +3558,8 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>16</v>
+      <c r="M52" s="3">
+        <v>100</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>16</v>
@@ -3456,8 +3576,8 @@
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,53 +3665,56 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E54" s="3">
         <v>242700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>251900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>240400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>249600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>249200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>159000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>156400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>140800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>142300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3601,8 +3727,8 @@
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
+      <c r="V54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,53 +3792,54 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E57" s="3">
         <v>21100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3721,8 +3852,8 @@
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,53 +3932,56 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E59" s="3">
         <v>25900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3857,8 +3994,8 @@
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -3866,53 +4003,56 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E60" s="3">
         <v>47000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3925,8 +4065,8 @@
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
+      <c r="V60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
@@ -3934,53 +4074,56 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E61" s="3">
         <v>53100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>52900</v>
       </c>
       <c r="G61" s="3">
         <v>52900</v>
       </c>
       <c r="H61" s="3">
+        <v>52900</v>
+      </c>
+      <c r="I61" s="3">
         <v>52800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>52600</v>
       </c>
       <c r="K61" s="3">
         <v>52600</v>
       </c>
       <c r="L61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="M61" s="3">
         <v>29400</v>
       </c>
       <c r="N61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="O61" s="3">
         <v>29300</v>
       </c>
       <c r="P61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="Q61" s="3">
         <v>29200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4002,40 +4145,43 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E62" s="3">
         <v>16200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>15500</v>
       </c>
       <c r="I62" s="3">
         <v>15500</v>
       </c>
       <c r="J62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K62" s="3">
         <v>19000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
@@ -4046,8 +4192,8 @@
       <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>16</v>
+      <c r="Q62" s="3">
+        <v>200</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>16</v>
@@ -4061,8 +4207,8 @@
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,53 +4429,56 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E66" s="3">
         <v>116300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>114000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>102500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>99700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>94200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4333,8 +4491,8 @@
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
+      <c r="V66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4546,11 +4714,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>7900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,53 +4811,56 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-152900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-134200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-128000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-110400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-84700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-68200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-50900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-41900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4699,8 +4873,8 @@
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,53 +5095,56 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>112100</v>
+      </c>
+      <c r="E76" s="3">
         <v>126400</v>
-      </c>
-      <c r="E76" s="3">
-        <v>137900</v>
       </c>
       <c r="F76" s="3">
         <v>137900</v>
       </c>
       <c r="G76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="H76" s="3">
         <v>150000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>157600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>86800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>93100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>102900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4971,8 +5157,8 @@
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
+      <c r="V76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,52 +5413,53 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>900</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
       </c>
       <c r="J83" s="3">
+        <v>900</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
@@ -5274,8 +5473,8 @@
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,53 +5837,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5682,8 +5899,8 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,53 +5937,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-900</v>
       </c>
       <c r="N91" s="3">
         <v>-900</v>
       </c>
       <c r="O91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5776,8 +5997,8 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,53 +6148,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E94" s="3">
         <v>3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-80500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-900</v>
       </c>
       <c r="N94" s="3">
         <v>-900</v>
       </c>
       <c r="O94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5980,8 +6210,8 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,53 +6530,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
-      </c>
-      <c r="E100" s="3">
-        <v>200</v>
       </c>
       <c r="F100" s="3">
         <v>200</v>
       </c>
       <c r="G100" s="3">
+        <v>200</v>
+      </c>
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>107900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>107800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6346,8 +6592,8 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,53 +6672,56 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-69100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>103400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6482,13 +6734,16 @@
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E8" s="3">
         <v>44500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>51100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>40800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E10" s="3">
         <v>35700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>42000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="3">
         <v>5200</v>
       </c>
-      <c r="E12" s="3">
-        <v>5300</v>
-      </c>
       <c r="F12" s="3">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="G12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H12" s="3">
         <v>4400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1900</v>
       </c>
       <c r="R12" s="3">
         <v>1900</v>
       </c>
       <c r="S12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1500</v>
       </c>
       <c r="W12" s="3">
         <v>1500</v>
       </c>
       <c r="X12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1156,29 +1176,29 @@
         <v>16</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>4500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1215,31 +1235,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E17" s="3">
         <v>65800</v>
       </c>
-      <c r="E17" s="3">
-        <v>70100</v>
-      </c>
       <c r="F17" s="3">
-        <v>69000</v>
+        <v>70000</v>
       </c>
       <c r="G17" s="3">
+        <v>68900</v>
+      </c>
+      <c r="H17" s="3">
         <v>58600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>55000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-21300</v>
+        <v>-15100</v>
       </c>
       <c r="E18" s="3">
-        <v>-19000</v>
+        <v>-21400</v>
       </c>
       <c r="F18" s="3">
-        <v>-6800</v>
+        <v>-18900</v>
       </c>
       <c r="G18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-17800</v>
       </c>
-      <c r="H18" s="3">
-        <v>-13000</v>
-      </c>
       <c r="I18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3600</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,43 +1512,44 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>1600</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>1800</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>1600</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>1600</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1530,76 +1564,79 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-17800</v>
+        <v>-13000</v>
       </c>
       <c r="E21" s="3">
-        <v>-15500</v>
+        <v>-19200</v>
       </c>
       <c r="F21" s="3">
-        <v>-3200</v>
+        <v>-16900</v>
       </c>
       <c r="G21" s="3">
-        <v>-14700</v>
+        <v>-5100</v>
       </c>
       <c r="H21" s="3">
-        <v>-9900</v>
+        <v>-16200</v>
       </c>
       <c r="I21" s="3">
-        <v>-11200</v>
+        <v>-11900</v>
       </c>
       <c r="J21" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-5300</v>
       </c>
       <c r="O21" s="3">
         <v>-5300</v>
       </c>
       <c r="P21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1621,8 +1658,11 @@
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1648,13 +1688,13 @@
         <v>1300</v>
       </c>
       <c r="K22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1000</v>
       </c>
       <c r="N22" s="3">
         <v>1000</v>
@@ -1669,125 +1709,131 @@
         <v>1000</v>
       </c>
       <c r="R22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
       </c>
       <c r="Y22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,43 +2398,46 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-1600</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-1800</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1600</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-1600</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2382,99 +2452,105 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,56 +2831,57 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E41" s="3">
         <v>18200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>88500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>105800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>119600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2807,8 +2894,8 @@
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
+      <c r="W41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -2816,35 +2903,38 @@
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E42" s="3">
         <v>76900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>100700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>110200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>114900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>127400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>141000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>61800</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2860,8 +2950,8 @@
       <c r="P42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2887,56 +2977,59 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25600</v>
+        <v>24800</v>
       </c>
       <c r="E43" s="3">
-        <v>30100</v>
+        <v>26500</v>
       </c>
       <c r="F43" s="3">
-        <v>38100</v>
+        <v>31100</v>
       </c>
       <c r="G43" s="3">
+        <v>39200</v>
+      </c>
+      <c r="H43" s="3">
         <v>25000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2949,8 +3042,8 @@
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -2958,56 +3051,59 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E44" s="3">
         <v>41300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>29200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>29300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>22500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7400</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3020,8 +3116,8 @@
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3029,56 +3125,59 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>11400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="3">
         <v>3600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4000</v>
       </c>
       <c r="L45" s="3">
         <v>4000</v>
       </c>
       <c r="M45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3091,8 +3190,8 @@
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
@@ -3100,56 +3199,59 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E46" s="3">
         <v>171600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>187400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>198400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>198100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>223100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>133400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>135200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>138000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>135400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>140800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3162,8 +3264,8 @@
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
+      <c r="W46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X46" s="3">
         <v>0</v>
@@ -3171,31 +3273,34 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3242,56 +3347,59 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E48" s="3">
         <v>33000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3304,8 +3412,8 @@
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3313,31 +3421,34 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E49" s="3">
         <v>21400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22300</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>16</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>16</v>
@@ -3351,8 +3462,8 @@
       <c r="N49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,13 +3643,16 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -3547,10 +3667,10 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3561,8 +3681,8 @@
       <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>16</v>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>16</v>
@@ -3579,8 +3699,8 @@
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,56 +3791,59 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E54" s="3">
         <v>226100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>242700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>251900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>240400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>249600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>249200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>159000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>156400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>158700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>140800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>142300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3730,8 +3856,8 @@
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
+      <c r="W54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X54" s="3">
         <v>0</v>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,56 +3923,57 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E57" s="3">
         <v>18100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3855,8 +3986,8 @@
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -3864,31 +3995,34 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3935,56 +4069,59 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26400</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
-        <v>25900</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>33200</v>
+        <v>7800</v>
       </c>
       <c r="G59" s="3">
-        <v>24500</v>
+        <v>6400</v>
       </c>
       <c r="H59" s="3">
-        <v>21900</v>
+        <v>4000</v>
       </c>
       <c r="I59" s="3">
-        <v>18200</v>
+        <v>2800</v>
       </c>
       <c r="J59" s="3">
+        <v>700</v>
+      </c>
+      <c r="K59" s="3">
         <v>21600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3997,8 +4134,8 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -4006,56 +4143,59 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E60" s="3">
         <v>44400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4068,8 +4208,8 @@
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
+      <c r="W60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X60" s="3">
         <v>0</v>
@@ -4077,56 +4217,59 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53200</v>
+        <v>69700</v>
       </c>
       <c r="E61" s="3">
-        <v>53100</v>
+        <v>69500</v>
       </c>
       <c r="F61" s="3">
-        <v>53000</v>
+        <v>69200</v>
       </c>
       <c r="G61" s="3">
-        <v>52900</v>
+        <v>68900</v>
       </c>
       <c r="H61" s="3">
-        <v>52900</v>
+        <v>69300</v>
       </c>
       <c r="I61" s="3">
-        <v>52800</v>
+        <v>69600</v>
       </c>
       <c r="J61" s="3">
+        <v>68200</v>
+      </c>
+      <c r="K61" s="3">
         <v>52700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>52600</v>
       </c>
       <c r="L61" s="3">
         <v>52600</v>
       </c>
       <c r="M61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="N61" s="3">
         <v>29400</v>
       </c>
       <c r="O61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="P61" s="3">
         <v>29300</v>
       </c>
       <c r="Q61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="R61" s="3">
         <v>29200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4148,43 +4291,46 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16300</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>15900</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="J62" s="3">
-        <v>15500</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14900</v>
-      </c>
-      <c r="N62" s="3">
-        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
@@ -4195,8 +4341,8 @@
       <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>16</v>
+      <c r="R62" s="3">
+        <v>200</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>16</v>
@@ -4210,8 +4356,8 @@
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,56 +4587,59 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E66" s="3">
         <v>113900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>116300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>99700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>94200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4494,8 +4652,8 @@
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
+      <c r="W66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X66" s="3">
         <v>0</v>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4717,11 +4885,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>7900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,56 +4985,59 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-189500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-174100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-152900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-134200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-128000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-110400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-98200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-84700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-68200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-50900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-41900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-23800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4876,8 +5050,8 @@
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,56 +5281,59 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E76" s="3">
         <v>112100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>126400</v>
-      </c>
-      <c r="F76" s="3">
-        <v>137900</v>
       </c>
       <c r="G76" s="3">
         <v>137900</v>
       </c>
       <c r="H76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="I76" s="3">
         <v>150000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>157600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>60500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>86800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>93100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-8600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5160,8 +5346,8 @@
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
+      <c r="W76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X76" s="3">
         <v>0</v>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,55 +5612,56 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
-        <v>900</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
       </c>
       <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
+      <c r="R83" s="3">
+        <v>100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>16</v>
@@ -5476,8 +5675,8 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,56 +6054,59 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5902,8 +6119,8 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,56 +6158,57 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-900</v>
       </c>
       <c r="O91" s="3">
         <v>-900</v>
       </c>
       <c r="P91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6000,8 +6221,8 @@
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,56 +6378,59 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E94" s="3">
         <v>22400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-80500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-900</v>
       </c>
       <c r="O94" s="3">
         <v>-900</v>
       </c>
       <c r="P94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6213,8 +6443,8 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,56 +6776,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>200</v>
       </c>
       <c r="G100" s="3">
         <v>200</v>
       </c>
       <c r="H100" s="3">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>107900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>107800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6595,8 +6841,8 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -6604,31 +6850,34 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6675,56 +6924,59 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E102" s="3">
         <v>8800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-69100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>103400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6737,13 +6989,16 @@
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E8" s="3">
         <v>45100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>44500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>51100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>62200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>42200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
         <v>9000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E10" s="3">
         <v>36100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>35700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E12" s="3">
         <v>5000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5200</v>
       </c>
       <c r="F12" s="3">
         <v>5200</v>
       </c>
       <c r="G12" s="3">
-        <v>4100</v>
+        <v>5200</v>
       </c>
       <c r="H12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I12" s="3">
         <v>4400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1900</v>
       </c>
       <c r="S12" s="3">
         <v>1900</v>
       </c>
       <c r="T12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1500</v>
       </c>
       <c r="X12" s="3">
         <v>1500</v>
       </c>
       <c r="Y12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,19 +1180,22 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="3">
-        <v>100</v>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="3">
         <v>100</v>
@@ -1190,18 +1209,18 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>4500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1217,8 +1236,8 @@
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1238,35 +1257,38 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
-        <v>1500</v>
-      </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E17" s="3">
         <v>60200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70000</v>
       </c>
-      <c r="G17" s="3">
-        <v>68900</v>
-      </c>
       <c r="H17" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I17" s="3">
         <v>58600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>56000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>53600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-17800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3600</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,16 +1545,17 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
@@ -1531,28 +1564,28 @@
         <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1567,79 +1600,82 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-16200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-5300</v>
       </c>
       <c r="P21" s="3">
         <v>-5300</v>
       </c>
       <c r="Q21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1661,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,13 +1730,13 @@
         <v>1300</v>
       </c>
       <c r="L22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1000</v>
       </c>
       <c r="O22" s="3">
         <v>1000</v>
@@ -1712,105 +1751,111 @@
         <v>1000</v>
       </c>
       <c r="S22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>300</v>
-      </c>
-      <c r="X22" s="3">
-        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1835,8 +1880,8 @@
       <c r="J24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1883,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,16 +2467,19 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
@@ -2419,28 +2488,28 @@
         <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2455,102 +2524,108 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,59 +2917,60 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E41" s="3">
         <v>12100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>88500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>98500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>119600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2897,8 +2983,8 @@
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
+      <c r="X41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -2906,38 +2992,41 @@
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E42" s="3">
         <v>70700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>76900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>100700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>110200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>114900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>127400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>141000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>61800</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2953,8 +3042,8 @@
       <c r="Q42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2980,59 +3069,62 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E43" s="3">
         <v>24800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>39200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3045,8 +3137,8 @@
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3054,59 +3146,62 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E44" s="3">
         <v>43600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>29200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7400</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3119,8 +3214,8 @@
       <c r="W44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3128,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3154,33 +3252,33 @@
       <c r="J45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="3">
         <v>3600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4000</v>
       </c>
       <c r="M45" s="3">
         <v>4000</v>
       </c>
       <c r="N45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3193,8 +3291,8 @@
       <c r="W45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="X45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3202,59 +3300,62 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E46" s="3">
         <v>157600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>171600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>198400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>187100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>198100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>223100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>133400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>135200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>127300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>138000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>135400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3267,8 +3368,8 @@
       <c r="W46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
+      <c r="X46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y46" s="3">
         <v>0</v>
@@ -3276,8 +3377,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3302,8 +3406,8 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3350,59 +3454,62 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E48" s="3">
         <v>33700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3415,8 +3522,8 @@
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3424,34 +3531,37 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E49" s="3">
         <v>21100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22300</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>16</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>16</v>
@@ -3465,8 +3575,8 @@
       <c r="O49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,16 +3762,19 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>400</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -3670,10 +3789,10 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3684,8 +3803,8 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>16</v>
+      <c r="O52" s="3">
+        <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>16</v>
@@ -3702,8 +3821,8 @@
       <c r="T52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,59 +3916,62 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>217100</v>
+      </c>
+      <c r="E54" s="3">
         <v>212900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>226100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>242700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>251900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>240400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>249600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>249200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>159000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>156400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>158700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>146500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>140800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>142300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3859,8 +3984,8 @@
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X54" s="3">
-        <v>0</v>
+      <c r="X54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y54" s="3">
         <v>0</v>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,59 +4053,60 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E57" s="3">
         <v>18600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3989,8 +4119,8 @@
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -3998,8 +4128,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4010,23 +4143,23 @@
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4072,59 +4205,62 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4137,8 +4273,8 @@
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4146,59 +4282,62 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E60" s="3">
         <v>38300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,8 +4350,8 @@
       <c r="W60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
+      <c r="X60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y60" s="3">
         <v>0</v>
@@ -4220,59 +4359,62 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E61" s="3">
         <v>69700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>69200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>68900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>68200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52700</v>
-      </c>
-      <c r="L61" s="3">
-        <v>52600</v>
       </c>
       <c r="M61" s="3">
         <v>52600</v>
       </c>
       <c r="N61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="O61" s="3">
         <v>29400</v>
       </c>
       <c r="P61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="Q61" s="3">
         <v>29300</v>
       </c>
       <c r="R61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="S61" s="3">
         <v>29200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4294,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4321,19 +4466,19 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>15500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>200</v>
@@ -4344,8 +4489,8 @@
       <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>16</v>
+      <c r="S62" s="3">
+        <v>200</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>16</v>
@@ -4359,8 +4504,8 @@
       <c r="W62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,59 +4744,62 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E66" s="3">
         <v>108000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>113900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>116300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>114000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>102500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>99700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>94200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>87000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4655,8 +4812,8 @@
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
+      <c r="X66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y66" s="3">
         <v>0</v>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4888,11 +5055,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>7900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,59 +5158,62 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-190000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-189500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-174100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-152900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-134200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-128000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-110400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-98200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-84700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-80300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-68200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-50900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-41900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-23800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5053,8 +5226,8 @@
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,59 +5466,62 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>112900</v>
+      </c>
+      <c r="E76" s="3">
         <v>104900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>112100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>137900</v>
       </c>
       <c r="H76" s="3">
         <v>137900</v>
       </c>
       <c r="I76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="J76" s="3">
         <v>150000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>157600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>60500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>62200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>93100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>102900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-8600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5349,8 +5534,8 @@
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
+      <c r="X76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y76" s="3">
         <v>0</v>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,58 +5810,59 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>900</v>
       </c>
       <c r="G83" s="3">
         <v>900</v>
       </c>
       <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
+      <c r="S83" s="3">
+        <v>100</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>16</v>
@@ -5678,8 +5876,8 @@
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,59 +6270,62 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6122,8 +6338,8 @@
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,59 +6378,60 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-900</v>
       </c>
       <c r="P91" s="3">
         <v>-900</v>
       </c>
       <c r="Q91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6224,8 +6444,8 @@
       <c r="W91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,59 +6607,62 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>22400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-80500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-900</v>
       </c>
       <c r="P94" s="3">
         <v>-900</v>
       </c>
       <c r="Q94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6446,8 +6675,8 @@
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6788,50 +7033,50 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>200</v>
       </c>
       <c r="H100" s="3">
         <v>200</v>
       </c>
       <c r="I100" s="3">
+        <v>200</v>
+      </c>
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>107900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>107800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6844,8 +7089,8 @@
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -6853,8 +7098,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,8 +7127,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6927,59 +7175,62 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-69100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>103400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1900</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6992,13 +7243,16 @@
       <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E8" s="3">
         <v>68700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>51100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>62200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>42000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E9" s="3">
         <v>13200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E10" s="3">
         <v>55500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>36100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E12" s="3">
         <v>5200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5200</v>
       </c>
       <c r="G12" s="3">
         <v>5200</v>
       </c>
       <c r="H12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I12" s="3">
         <v>4200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1900</v>
       </c>
       <c r="T12" s="3">
         <v>1900</v>
       </c>
       <c r="U12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1500</v>
       </c>
       <c r="Y12" s="3">
         <v>1500</v>
       </c>
       <c r="Z12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,22 +1200,25 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
@@ -1212,18 +1232,18 @@
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>4500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1239,8 +1259,8 @@
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1260,38 +1280,41 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E17" s="3">
         <v>68900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>65800</v>
       </c>
-      <c r="G17" s="3">
-        <v>70000</v>
-      </c>
       <c r="H17" s="3">
+        <v>70100</v>
+      </c>
+      <c r="I17" s="3">
         <v>69000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-18900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3600</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1555,10 +1589,10 @@
         <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
@@ -1567,28 +1601,28 @@
         <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1603,82 +1637,85 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-16900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-5300</v>
       </c>
       <c r="Q21" s="3">
         <v>-5300</v>
       </c>
       <c r="R21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="S21" s="3">
         <v>-3900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1700,8 +1737,11 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1733,13 +1773,13 @@
         <v>1300</v>
       </c>
       <c r="M22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1000</v>
       </c>
       <c r="P22" s="3">
         <v>1000</v>
@@ -1754,108 +1794,114 @@
         <v>1000</v>
       </c>
       <c r="T22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U22" s="3">
         <v>1100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
       </c>
       <c r="AA22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1883,8 +1929,8 @@
       <c r="K24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2479,10 +2549,10 @@
         <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
@@ -2491,28 +2561,28 @@
         <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2527,105 +2597,111 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,62 +3004,63 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E41" s="3">
         <v>11400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>88500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>98500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>105800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>109500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>119600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2986,8 +3073,8 @@
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
+      <c r="Y41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z41" s="3">
         <v>0</v>
@@ -2995,41 +3082,44 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E42" s="3">
         <v>64300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>70700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>76900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>110200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>114900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>127400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>141000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>61800</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3045,8 +3135,8 @@
       <c r="R42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3072,62 +3162,65 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E43" s="3">
         <v>41400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3140,8 +3233,8 @@
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3149,62 +3242,65 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E44" s="3">
         <v>39300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>43600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>41300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>26100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3217,8 +3313,8 @@
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -3226,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3255,33 +3354,33 @@
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3">
         <v>3600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4000</v>
       </c>
       <c r="N45" s="3">
         <v>4000</v>
       </c>
       <c r="O45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3294,8 +3393,8 @@
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -3303,62 +3402,65 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E46" s="3">
         <v>161400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>157600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>171600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>198400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>187100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>198100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>223100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>133400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>135200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>127300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>138000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>135400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>140800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3371,8 +3473,8 @@
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y46" s="3">
-        <v>0</v>
+      <c r="Y46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z46" s="3">
         <v>0</v>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3409,8 +3514,8 @@
       <c r="K47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3457,62 +3562,65 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E48" s="3">
         <v>34400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3525,8 +3633,8 @@
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3534,37 +3642,40 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E49" s="3">
         <v>20900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22300</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>16</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>16</v>
@@ -3578,8 +3689,8 @@
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3774,10 +3894,10 @@
         <v>400</v>
       </c>
       <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -3792,10 +3912,10 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -3806,8 +3926,8 @@
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>16</v>
+      <c r="P52" s="3">
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>16</v>
@@ -3824,8 +3944,8 @@
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,62 +4042,65 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E54" s="3">
         <v>217100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>212900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>226100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>242700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>251900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>240400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>249600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>249200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>159000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>156400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>158700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>146500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>140800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>142300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3987,8 +4113,8 @@
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y54" s="3">
-        <v>0</v>
+      <c r="Y54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z54" s="3">
         <v>0</v>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,62 +4184,63 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E57" s="3">
         <v>10500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4122,8 +4253,8 @@
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -4131,13 +4262,16 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -4146,23 +4280,23 @@
         <v>400</v>
       </c>
       <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4208,62 +4342,65 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4276,8 +4413,8 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4285,62 +4422,65 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E60" s="3">
         <v>34900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4353,8 +4493,8 @@
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
+      <c r="Y60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z60" s="3">
         <v>0</v>
@@ -4362,62 +4502,65 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E61" s="3">
         <v>69200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>69500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>69200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>68900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>68200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52700</v>
-      </c>
-      <c r="M61" s="3">
-        <v>52600</v>
       </c>
       <c r="N61" s="3">
         <v>52600</v>
       </c>
       <c r="O61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="P61" s="3">
         <v>29400</v>
       </c>
       <c r="Q61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="R61" s="3">
         <v>29300</v>
       </c>
       <c r="S61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="T61" s="3">
         <v>29200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4469,19 +4615,19 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>200</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
@@ -4492,8 +4638,8 @@
       <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>16</v>
+      <c r="T62" s="3">
+        <v>200</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>16</v>
@@ -4507,8 +4653,8 @@
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,62 +4902,65 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E66" s="3">
         <v>104200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>113900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>116300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>114000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>99700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>98500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>94200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>87000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4815,8 +4973,8 @@
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y66" s="3">
-        <v>0</v>
+      <c r="Y66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z66" s="3">
         <v>0</v>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5058,11 +5226,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>7900</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,62 +5332,65 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-205900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-190000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-189500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-174100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-152900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-134200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-128000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-110400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-84700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-80300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-68200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-50900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-23800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5229,8 +5403,8 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,62 +5652,65 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E76" s="3">
         <v>112900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>112100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>137900</v>
       </c>
       <c r="I76" s="3">
         <v>137900</v>
       </c>
       <c r="J76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="K76" s="3">
         <v>150000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>157600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>60500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>93100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>102900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-8600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5537,8 +5723,8 @@
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
+      <c r="Y76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z76" s="3">
         <v>0</v>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,61 +6009,62 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>900</v>
       </c>
       <c r="I83" s="3">
+        <v>900</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
+      <c r="T83" s="3">
+        <v>100</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
@@ -5879,8 +6078,8 @@
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,62 +6487,65 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6341,8 +6558,8 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,62 +6599,63 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-900</v>
       </c>
       <c r="Q91" s="3">
         <v>-900</v>
       </c>
       <c r="R91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6447,8 +6668,8 @@
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,62 +6837,65 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-900</v>
       </c>
       <c r="Q94" s="3">
         <v>-900</v>
       </c>
       <c r="R94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6678,8 +6908,8 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,62 +7267,65 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>200</v>
       </c>
       <c r="I100" s="3">
         <v>200</v>
       </c>
       <c r="J100" s="3">
+        <v>200</v>
+      </c>
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>107900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>107800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7092,8 +7338,8 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7130,8 +7379,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7178,62 +7427,65 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-69100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>103400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7246,13 +7498,16 @@
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E8" s="3">
         <v>52600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>68700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>51100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
         <v>10700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E10" s="3">
         <v>41900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>35700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E12" s="3">
         <v>5600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1900</v>
       </c>
       <c r="U12" s="3">
         <v>1900</v>
       </c>
       <c r="V12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1500</v>
       </c>
       <c r="Z12" s="3">
         <v>1500</v>
       </c>
       <c r="AA12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,20 +1220,23 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1235,18 +1255,18 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>4500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1262,8 +1282,8 @@
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1283,41 +1303,44 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E17" s="3">
         <v>68200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>68900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>60200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>65800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>70100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>69000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>53600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3600</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1592,10 +1626,10 @@
         <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -1604,28 +1638,28 @@
         <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>-100</v>
       </c>
       <c r="M20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1640,85 +1674,88 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-5300</v>
       </c>
       <c r="R21" s="3">
         <v>-5300</v>
       </c>
       <c r="S21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="T21" s="3">
         <v>-3900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1776,13 +1816,13 @@
         <v>1300</v>
       </c>
       <c r="N22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1000</v>
       </c>
       <c r="Q22" s="3">
         <v>1000</v>
@@ -1797,111 +1837,117 @@
         <v>1000</v>
       </c>
       <c r="U22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V22" s="3">
         <v>1100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>200</v>
       </c>
       <c r="AB22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +1978,8 @@
       <c r="L24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2552,10 +2622,10 @@
         <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
@@ -2564,28 +2634,28 @@
         <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
       </c>
       <c r="M32" s="3">
+        <v>100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2600,108 +2670,114 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,65 +3091,66 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E41" s="3">
         <v>13400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>98500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>105800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>109500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>119600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3076,8 +3163,8 @@
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
+      <c r="Z41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA41" s="3">
         <v>0</v>
@@ -3085,44 +3172,47 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E42" s="3">
         <v>62700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>64300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>76900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>100700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>110200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>114900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>127400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>141000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>61800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3138,8 +3228,8 @@
       <c r="S42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3165,65 +3255,68 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E43" s="3">
         <v>31700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3236,8 +3329,8 @@
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3245,65 +3338,68 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E44" s="3">
         <v>37900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>39300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>43600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>41300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>29300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>26100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>10400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7400</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3316,8 +3412,8 @@
       <c r="Y44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3357,33 +3456,33 @@
       <c r="L45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" s="3">
         <v>3600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>4000</v>
       </c>
       <c r="O45" s="3">
         <v>4000</v>
       </c>
       <c r="P45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3396,8 +3495,8 @@
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
+      <c r="Z45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3405,65 +3504,68 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E46" s="3">
         <v>149400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>157600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>171600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>187400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>198400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>187100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>198100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>223100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>133400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>127900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>135200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>127300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>138000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>135400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>140800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36500</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3476,8 +3578,8 @@
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
+      <c r="Z46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA46" s="3">
         <v>0</v>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3517,8 +3622,8 @@
       <c r="L47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3565,65 +3670,68 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E48" s="3">
         <v>35400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3636,8 +3744,8 @@
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3645,40 +3753,43 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E49" s="3">
         <v>20700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22300</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>16</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>16</v>
@@ -3692,8 +3803,8 @@
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,22 +4002,25 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
+        <v>400</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3915,10 +4035,10 @@
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -3929,8 +4049,8 @@
       <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>16</v>
+      <c r="Q52" s="3">
+        <v>100</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>16</v>
@@ -3947,8 +4067,8 @@
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,65 +4168,68 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>206400</v>
+      </c>
+      <c r="E54" s="3">
         <v>205800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>217100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>212900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>226100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>242700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>251900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>240400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>249600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>249200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>159000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>156400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>158700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>146500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>140800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>137600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>142300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4116,8 +4242,8 @@
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z54" s="3">
-        <v>0</v>
+      <c r="Z54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA54" s="3">
         <v>0</v>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,65 +4315,66 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4256,8 +4387,8 @@
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -4265,16 +4396,19 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
@@ -4283,23 +4417,23 @@
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4345,8 +4479,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4354,56 +4491,56 @@
         <v>200</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4416,8 +4553,8 @@
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4425,65 +4562,68 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E60" s="3">
         <v>33200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4496,8 +4636,8 @@
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
+      <c r="Z60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA60" s="3">
         <v>0</v>
@@ -4505,65 +4645,68 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E61" s="3">
         <v>67300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>69700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>69500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>68900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>68200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>52600</v>
       </c>
       <c r="O61" s="3">
         <v>52600</v>
       </c>
       <c r="P61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="Q61" s="3">
         <v>29400</v>
       </c>
       <c r="R61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="S61" s="3">
         <v>29300</v>
       </c>
       <c r="T61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="U61" s="3">
         <v>29200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4618,19 +4764,19 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
@@ -4641,8 +4787,8 @@
       <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>16</v>
+      <c r="U62" s="3">
+        <v>200</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>16</v>
@@ -4656,8 +4802,8 @@
       <c r="Y62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,65 +5060,68 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E66" s="3">
         <v>100500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>104200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>116300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>99700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>94200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>87000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4976,8 +5134,8 @@
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z66" s="3">
-        <v>0</v>
+      <c r="Z66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA66" s="3">
         <v>0</v>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5229,11 +5397,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>7900</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,65 +5506,68 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-223300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-205900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-190000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-189500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-174100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-152900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-134200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-128000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-84700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-80300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-68200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-41900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-23800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5406,8 +5580,8 @@
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,65 +5838,68 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E76" s="3">
         <v>105300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>112900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>104900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>112100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>126400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>137900</v>
       </c>
       <c r="J76" s="3">
         <v>137900</v>
       </c>
       <c r="K76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="L76" s="3">
         <v>150000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>157600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>62200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>86800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>93100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-8600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5726,8 +5912,8 @@
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
+      <c r="Z76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA76" s="3">
         <v>0</v>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,64 +6208,65 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>900</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
       </c>
       <c r="J83" s="3">
+        <v>900</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
       </c>
       <c r="R83" s="3">
+        <v>300</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
+      <c r="U83" s="3">
+        <v>100</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
@@ -6081,8 +6280,8 @@
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,65 +6704,68 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6561,8 +6778,8 @@
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,65 +6820,66 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-900</v>
       </c>
       <c r="R91" s="3">
         <v>-900</v>
       </c>
       <c r="S91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6671,8 +6892,8 @@
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,65 +7067,68 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>22400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-64000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-900</v>
       </c>
       <c r="R94" s="3">
         <v>-900</v>
       </c>
       <c r="S94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6911,8 +7141,8 @@
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6982,8 +7216,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,65 +7513,68 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>200</v>
       </c>
       <c r="J100" s="3">
         <v>200</v>
       </c>
       <c r="K100" s="3">
+        <v>200</v>
+      </c>
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>107900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>107800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7341,8 +7587,8 @@
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7382,8 +7631,8 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7430,65 +7679,68 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-69100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>103400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1900</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7501,13 +7753,16 @@
       <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E8" s="3">
         <v>50200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>52600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>68700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>44500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>51100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>62200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>40800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>21600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E9" s="3">
         <v>10500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E10" s="3">
         <v>39700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>55500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>15400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E12" s="3">
         <v>4700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1900</v>
       </c>
       <c r="W12" s="3">
         <v>1900</v>
       </c>
       <c r="X12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>1500</v>
       </c>
       <c r="AB12" s="3">
         <v>1500</v>
       </c>
       <c r="AC12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,22 +1259,25 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
@@ -1281,18 +1300,18 @@
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1308,8 +1327,8 @@
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1329,47 +1348,50 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E17" s="3">
         <v>64900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>68200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>68900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>60200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>65800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>70100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>44400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3600</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1666,10 +1699,10 @@
         <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
@@ -1678,28 +1711,28 @@
         <v>-100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1714,91 +1747,94 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-5300</v>
       </c>
       <c r="T21" s="3">
         <v>-5300</v>
       </c>
       <c r="U21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="V21" s="3">
         <v>-3900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1820,13 +1856,16 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E22" s="3">
         <v>1300</v>
@@ -1862,13 +1901,13 @@
         <v>1300</v>
       </c>
       <c r="P22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1000</v>
       </c>
       <c r="S22" s="3">
         <v>1000</v>
@@ -1883,117 +1922,123 @@
         <v>1000</v>
       </c>
       <c r="W22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X22" s="3">
         <v>1100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>300</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
       </c>
       <c r="AD22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2030,8 +2075,8 @@
       <c r="N24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2078,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2698,10 +2767,10 @@
         <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
@@ -2710,28 +2779,28 @@
         <v>100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2746,114 +2815,120 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,71 +3264,72 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>98500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>105800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>109500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>119600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3256,8 +3342,8 @@
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB41" s="3">
-        <v>0</v>
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC41" s="3">
         <v>0</v>
@@ -3265,50 +3351,53 @@
       <c r="AD41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E42" s="3">
         <v>49700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>61200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>62700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>64300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>70700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>76900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>110200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>114900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>127400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>141000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>61800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3324,8 +3413,8 @@
       <c r="U42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3351,71 +3440,74 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E43" s="3">
         <v>33600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>41400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3428,8 +3520,8 @@
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3437,71 +3529,74 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E44" s="3">
         <v>41400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>42400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>37900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>39300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>43600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>41300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>29200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>29300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>26100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3514,8 +3609,8 @@
       <c r="AA44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
@@ -3523,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3561,33 +3659,33 @@
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="3">
         <v>3600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>4000</v>
       </c>
       <c r="Q45" s="3">
         <v>4000</v>
       </c>
       <c r="R45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3600,8 +3698,8 @@
       <c r="AA45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3609,71 +3707,74 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E46" s="3">
         <v>138000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>147600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>161400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>157600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>171600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>187400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>198400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>187100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>198100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>223100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>133400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>127900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>135200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>127300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>138000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>135400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>140800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>36500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3686,8 +3787,8 @@
       <c r="AA46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB46" s="3">
-        <v>0</v>
+      <c r="AB46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC46" s="3">
         <v>0</v>
@@ -3695,8 +3796,11 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3733,8 +3837,8 @@
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3781,71 +3885,74 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>37800</v>
+        <v>37400</v>
       </c>
       <c r="E48" s="3">
         <v>37800</v>
       </c>
       <c r="F48" s="3">
+        <v>37800</v>
+      </c>
+      <c r="G48" s="3">
         <v>35400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3858,8 +3965,8 @@
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3867,46 +3974,49 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E49" s="3">
         <v>20200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22300</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
@@ -3920,8 +4030,8 @@
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,28 +4241,31 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
       </c>
       <c r="H52" s="3">
+        <v>400</v>
+      </c>
+      <c r="I52" s="3">
         <v>500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -4161,10 +4280,10 @@
         <v>100</v>
       </c>
       <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4175,8 +4294,8 @@
       <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>16</v>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>16</v>
@@ -4193,8 +4312,8 @@
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,71 +4419,74 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E54" s="3">
         <v>196600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>206400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>205800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>217100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>212900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>226100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>242700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>251900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>240400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>249600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>249200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>159000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>156400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>158700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>146500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>140800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>137600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>142300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4374,8 +4499,8 @@
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB54" s="3">
-        <v>0</v>
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC54" s="3">
         <v>0</v>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,71 +4576,72 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E57" s="3">
         <v>16100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4524,8 +4654,8 @@
       <c r="AA57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -4533,22 +4663,25 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>400</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
@@ -4557,23 +4690,23 @@
         <v>400</v>
       </c>
       <c r="J58" s="3">
+        <v>400</v>
+      </c>
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4619,13 +4752,16 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -4634,56 +4770,56 @@
         <v>200</v>
       </c>
       <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4696,8 +4832,8 @@
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -4705,71 +4841,74 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E60" s="3">
         <v>40900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>44400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4782,8 +4921,8 @@
       <c r="AA60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB60" s="3">
-        <v>0</v>
+      <c r="AB60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC60" s="3">
         <v>0</v>
@@ -4791,71 +4930,74 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E61" s="3">
         <v>66500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>66900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>67300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>69200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>68900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>69300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>68200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52700</v>
-      </c>
-      <c r="P61" s="3">
-        <v>52600</v>
       </c>
       <c r="Q61" s="3">
         <v>52600</v>
       </c>
       <c r="R61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="S61" s="3">
         <v>29400</v>
       </c>
       <c r="T61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="U61" s="3">
         <v>29300</v>
       </c>
       <c r="V61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="W61" s="3">
         <v>29200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4877,13 +5019,16 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -4916,19 +5061,19 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>15500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>200</v>
       </c>
       <c r="T62" s="3">
         <v>200</v>
@@ -4939,8 +5084,8 @@
       <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>16</v>
+      <c r="W62" s="3">
+        <v>200</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>16</v>
@@ -4954,8 +5099,8 @@
       <c r="AA62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,71 +5375,74 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E66" s="3">
         <v>107400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>104200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>108000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>116300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>102500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>99700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>91600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>98500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>87000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>39400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5298,8 +5455,8 @@
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB66" s="3">
-        <v>0</v>
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC66" s="3">
         <v>0</v>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5571,11 +5738,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>7900</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,71 +5853,74 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-249000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-239600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-223300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-205900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-190000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-189500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-174100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-152900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-134200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-128000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-110400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-98200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-84700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-80300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-68200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-50900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-41900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-28900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-23800</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5760,8 +5933,8 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB72" s="3">
-        <v>0</v>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,71 +6209,74 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E76" s="3">
         <v>89200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>97600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>105300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>112900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>104900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>112100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>126400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>137900</v>
       </c>
       <c r="L76" s="3">
         <v>137900</v>
       </c>
       <c r="M76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="N76" s="3">
         <v>150000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>157600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>60500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>93100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>97400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>102900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-8600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6104,8 +6289,8 @@
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC76" s="3">
         <v>0</v>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,70 +6605,71 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
       </c>
       <c r="L83" s="3">
+        <v>900</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
       </c>
       <c r="T83" s="3">
+        <v>300</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>16</v>
+      <c r="W83" s="3">
+        <v>100</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>16</v>
@@ -6485,8 +6683,8 @@
       <c r="AA83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,71 +7137,74 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7001,8 +7217,8 @@
       <c r="AA89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,71 +7261,72 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-900</v>
       </c>
       <c r="T91" s="3">
         <v>-900</v>
       </c>
       <c r="U91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7119,8 +7339,8 @@
       <c r="AA91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,71 +7526,74 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E94" s="3">
         <v>8700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>22400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-80500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-900</v>
       </c>
       <c r="T94" s="3">
         <v>-900</v>
       </c>
       <c r="U94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7377,8 +7606,8 @@
       <c r="AA94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7689,8 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,71 +8004,74 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>200</v>
       </c>
       <c r="L100" s="3">
         <v>200</v>
       </c>
       <c r="M100" s="3">
+        <v>200</v>
+      </c>
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>107900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>107800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7839,8 +8084,8 @@
       <c r="AA100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -7848,8 +8093,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7886,8 +8134,8 @@
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7934,71 +8182,74 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-69100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>103400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8011,13 +8262,16 @@
       <c r="AA102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>TMCI</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E8" s="3">
         <v>62500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>50200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>52600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>68700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>44500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>62200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>40800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E9" s="3">
         <v>12100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E10" s="3">
         <v>50400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>39700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>55500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>17400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="3">
         <v>4500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1900</v>
       </c>
       <c r="X12" s="3">
         <v>1900</v>
       </c>
       <c r="Y12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1500</v>
       </c>
       <c r="AC12" s="3">
         <v>1500</v>
       </c>
       <c r="AD12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE12" s="3">
         <v>1000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,20 +1279,23 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>2700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1303,18 +1323,18 @@
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>4500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1330,8 +1350,8 @@
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1351,50 +1371,53 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>900</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E17" s="3">
         <v>68400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>68200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>68900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>60200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>65800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>58600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>44400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>39000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3600</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,13 +1714,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1702,10 +1736,10 @@
         <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1714,28 +1748,28 @@
         <v>-100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1750,94 +1784,97 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-19200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7800</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-5300</v>
       </c>
       <c r="U21" s="3">
         <v>-5300</v>
       </c>
       <c r="V21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="W21" s="3">
         <v>-3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1859,16 +1896,19 @@
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1300</v>
       </c>
       <c r="F22" s="3">
         <v>1300</v>
@@ -1904,13 +1944,13 @@
         <v>1300</v>
       </c>
       <c r="Q22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1000</v>
       </c>
       <c r="T22" s="3">
         <v>1000</v>
@@ -1925,120 +1965,126 @@
         <v>1000</v>
       </c>
       <c r="X22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>200</v>
       </c>
       <c r="AD22" s="3">
         <v>200</v>
       </c>
       <c r="AE22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2078,8 +2124,8 @@
       <c r="O24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,13 +2816,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -2770,10 +2840,10 @@
         <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -2782,28 +2852,28 @@
         <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -2818,117 +2888,123 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,74 +3351,75 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E41" s="3">
         <v>10700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>88500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>101500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>98500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>105800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>109500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>119600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3345,8 +3432,8 @@
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -3354,53 +3441,56 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E42" s="3">
         <v>37700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>49700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>62700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>64300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>70700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>76900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>110200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>114900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>127400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>141000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>61800</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3416,8 +3506,8 @@
       <c r="V42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3443,74 +3533,77 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E43" s="3">
         <v>42500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3523,8 +3616,8 @@
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3532,74 +3625,77 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E44" s="3">
         <v>36000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>42400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>37900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>39300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>43600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>41300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>35900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>29200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>29300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>26100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>16800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7400</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3612,8 +3708,8 @@
       <c r="AB44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3662,33 +3761,33 @@
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4000</v>
       </c>
       <c r="R45" s="3">
         <v>4000</v>
       </c>
       <c r="S45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3701,8 +3800,8 @@
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -3710,74 +3809,77 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E46" s="3">
         <v>132100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>138000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>147600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>149400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>161400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>157600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>171600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>187400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>198400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>187100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>198100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>223100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>133400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>127900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>135200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>127300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>138000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>135400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>140800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>36500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3790,8 +3892,8 @@
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC46" s="3">
-        <v>0</v>
+      <c r="AC46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD46" s="3">
         <v>0</v>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3840,8 +3945,8 @@
       <c r="O47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3888,74 +3993,77 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E48" s="3">
         <v>37400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>37800</v>
       </c>
       <c r="F48" s="3">
         <v>37800</v>
       </c>
       <c r="G48" s="3">
+        <v>37800</v>
+      </c>
+      <c r="H48" s="3">
         <v>35400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3968,8 +4076,8 @@
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -3977,49 +4085,52 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E49" s="3">
         <v>19900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22300</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
@@ -4033,8 +4144,8 @@
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,31 +4361,34 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
       </c>
       <c r="I52" s="3">
+        <v>400</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -4283,10 +4403,10 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -4297,8 +4417,8 @@
       <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>16</v>
+      <c r="T52" s="3">
+        <v>100</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>16</v>
@@ -4315,8 +4435,8 @@
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,74 +4545,77 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E54" s="3">
         <v>190600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>196600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>206400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>205800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>217100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>212900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>226100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>242700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>251900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>240400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>249600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>249200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>159000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>156400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>158700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>146500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>140800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>137600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>142300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4502,8 +4628,8 @@
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC54" s="3">
-        <v>0</v>
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD54" s="3">
         <v>0</v>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,74 +4707,75 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4657,8 +4788,8 @@
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4666,25 +4797,28 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
@@ -4693,23 +4827,23 @@
         <v>400</v>
       </c>
       <c r="K58" s="3">
+        <v>400</v>
+      </c>
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4755,16 +4889,19 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>200</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -4773,56 +4910,56 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4835,8 +4972,8 @@
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -4844,74 +4981,77 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E60" s="3">
         <v>30600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>15400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4924,8 +5064,8 @@
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC60" s="3">
-        <v>0</v>
+      <c r="AC60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -4933,74 +5073,77 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E61" s="3">
         <v>69600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>66500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>66900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>67300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>68900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>69600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>68200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>52700</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>52600</v>
       </c>
       <c r="R61" s="3">
         <v>52600</v>
       </c>
       <c r="S61" s="3">
-        <v>29400</v>
+        <v>52600</v>
       </c>
       <c r="T61" s="3">
         <v>29400</v>
       </c>
       <c r="U61" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="V61" s="3">
         <v>29300</v>
       </c>
       <c r="W61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="X61" s="3">
         <v>29200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5031,7 +5177,7 @@
         <v>3000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -5064,19 +5210,19 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>15500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -5087,8 +5233,8 @@
       <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>16</v>
+      <c r="X62" s="3">
+        <v>200</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>16</v>
@@ -5102,8 +5248,8 @@
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,74 +5533,77 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E66" s="3">
         <v>103200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>107400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>104200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>116300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>114000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>102500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>99700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>91600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>98500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>94200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>40200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5458,8 +5616,8 @@
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC66" s="3">
-        <v>0</v>
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD66" s="3">
         <v>0</v>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5741,11 +5909,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>7900</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,74 +6027,77 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-267000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-249000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-239600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-223300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-205900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-190000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-189500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-174100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-152900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-134200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-110400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-98200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-84700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-80300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-68200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-50900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-41900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-35300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-28900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-23800</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5936,8 +6110,8 @@
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD72" s="3">
         <v>0</v>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,74 +6395,77 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E76" s="3">
         <v>87300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>89200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>97600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>105300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>112900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>104900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>112100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>126400</v>
-      </c>
-      <c r="L76" s="3">
-        <v>137900</v>
       </c>
       <c r="M76" s="3">
         <v>137900</v>
       </c>
       <c r="N76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="O76" s="3">
         <v>150000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>157600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>60500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>86800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>93100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>97400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>102900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6292,8 +6478,8 @@
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD76" s="3">
         <v>0</v>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,73 +6804,74 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>16</v>
+      <c r="X83" s="3">
+        <v>100</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>16</v>
@@ -6686,8 +6885,8 @@
       <c r="AB83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,74 +7354,77 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7220,8 +7437,8 @@
       <c r="AB89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,74 +7482,75 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-900</v>
       </c>
       <c r="U91" s="3">
         <v>-900</v>
       </c>
       <c r="V91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7342,8 +7563,8 @@
       <c r="AB91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,74 +7756,77 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E94" s="3">
         <v>9700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-80500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-900</v>
       </c>
       <c r="U94" s="3">
         <v>-900</v>
       </c>
       <c r="V94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7609,8 +7839,8 @@
       <c r="AB94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7692,8 +7926,8 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,74 +8250,77 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>200</v>
       </c>
       <c r="M100" s="3">
         <v>200</v>
       </c>
       <c r="N100" s="3">
+        <v>200</v>
+      </c>
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>107900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>107800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8087,8 +8333,8 @@
       <c r="AB100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8137,8 +8386,8 @@
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8185,74 +8434,77 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-69100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>103400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8265,13 +8517,16 @@
       <c r="AB102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>
